--- a/data/gravel/Surly Karate Monkey 2025.xlsx
+++ b/data/gravel/Surly Karate Monkey 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9888FBEE-4250-8447-8B1F-3444A1923422}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0241C84-D0EA-6B43-B400-0C3B1DE4D1C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5980" yWindow="500" windowWidth="19740" windowHeight="16740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -352,13 +352,13 @@
     <t>flat bar</t>
   </si>
   <si>
+    <t>external</t>
+  </si>
+  <si>
+    <t>internal</t>
+  </si>
+  <si>
     <t>142/148</t>
-  </si>
-  <si>
-    <t>external</t>
-  </si>
-  <si>
-    <t>internal</t>
   </si>
 </sst>
 </file>
@@ -1377,7 +1377,7 @@
         <v>46</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.3">
@@ -1459,7 +1459,7 @@
         <v>57</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
@@ -1467,7 +1467,7 @@
         <v>58</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">

--- a/data/gravel/Surly Karate Monkey 2025.xlsx
+++ b/data/gravel/Surly Karate Monkey 2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0241C84-D0EA-6B43-B400-0C3B1DE4D1C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EA57E60-A0E6-474E-B01E-2236CBE35F1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5980" yWindow="500" windowWidth="19740" windowHeight="16740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -358,7 +358,7 @@
     <t>internal</t>
   </si>
   <si>
-    <t>142/148</t>
+    <t>142/148 gnot boost</t>
   </si>
 </sst>
 </file>

--- a/data/gravel/Surly Karate Monkey 2025.xlsx
+++ b/data/gravel/Surly Karate Monkey 2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EA57E60-A0E6-474E-B01E-2236CBE35F1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD06B02C-2981-294A-8AF1-3052C4BD3E48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5980" yWindow="500" windowWidth="19740" windowHeight="16740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="114">
   <si>
     <t>brand</t>
   </si>
@@ -359,6 +359,9 @@
   </si>
   <si>
     <t>142/148 gnot boost</t>
+  </si>
+  <si>
+    <t>https://surlybikes.com/cdn/shop/files/20200915_SUR_KarateMonkey_VanityPhotos_507744_034.jpg?v=1742144517&amp;width=1780</t>
   </si>
 </sst>
 </file>
@@ -744,6 +747,11 @@
         <v>107</v>
       </c>
     </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>113</v>
+      </c>
+    </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>6</v>

--- a/data/gravel/Surly Karate Monkey 2025.xlsx
+++ b/data/gravel/Surly Karate Monkey 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD06B02C-2981-294A-8AF1-3052C4BD3E48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D777CA6C-EEA0-A04F-8A5A-B775ADAC4E20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5980" yWindow="500" windowWidth="19740" windowHeight="16740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="116">
   <si>
     <t>brand</t>
   </si>
@@ -362,6 +362,12 @@
   </si>
   <si>
     <t>https://surlybikes.com/cdn/shop/files/20200915_SUR_KarateMonkey_VanityPhotos_507744_034.jpg?v=1742144517&amp;width=1780</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Bloomington, Minnesota, USA</t>
   </si>
 </sst>
 </file>
@@ -701,7 +707,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H70"/>
+  <dimension ref="A1:H71"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1570,6 +1576,14 @@
         <v>76</v>
       </c>
     </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>114</v>
+      </c>
+      <c r="B71" t="s">
+        <v>115</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/data/gravel/Surly Karate Monkey 2025.xlsx
+++ b/data/gravel/Surly Karate Monkey 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D777CA6C-EEA0-A04F-8A5A-B775ADAC4E20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C62EA7CF-29C3-7A46-B370-4BF999C66354}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5980" yWindow="500" windowWidth="19740" windowHeight="16740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="122">
   <si>
     <t>brand</t>
   </si>
@@ -368,6 +368,24 @@
   </si>
   <si>
     <t>Bloomington, Minnesota, USA</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -707,7 +725,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H71"/>
+  <dimension ref="A1:H77"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1404,183 +1422,213 @@
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>48</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>99</v>
+        <v>116</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>49</v>
+        <v>117</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>50</v>
-      </c>
-      <c r="B49">
-        <v>30.9</v>
+        <v>118</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>51</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>98</v>
+        <v>119</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>52</v>
-      </c>
-      <c r="B51">
-        <v>32</v>
+        <v>120</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>53</v>
-      </c>
-      <c r="B52">
-        <v>36</v>
+        <v>121</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>54</v>
-      </c>
-      <c r="B53">
-        <v>203</v>
+        <v>48</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>55</v>
-      </c>
-      <c r="B54">
-        <v>180</v>
+        <v>49</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>56</v>
+        <v>50</v>
+      </c>
+      <c r="B55">
+        <v>30.9</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>110</v>
+        <v>98</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>58</v>
-      </c>
-      <c r="B57" s="2" t="s">
-        <v>111</v>
+        <v>52</v>
+      </c>
+      <c r="B57">
+        <v>32</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>59</v>
+        <v>53</v>
+      </c>
+      <c r="B58">
+        <v>36</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>60</v>
+        <v>54</v>
+      </c>
+      <c r="B59">
+        <v>203</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="B60">
-        <v>2</v>
+        <v>180</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>62</v>
-      </c>
-      <c r="B61">
-        <v>1</v>
+        <v>56</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>63</v>
+        <v>57</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>64</v>
-      </c>
-      <c r="B63">
-        <v>3</v>
+        <v>58</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>65</v>
-      </c>
-      <c r="B64" s="2" t="s">
-        <v>98</v>
+        <v>59</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>66</v>
-      </c>
-      <c r="B65" s="2" t="s">
-        <v>98</v>
+        <v>60</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>67</v>
-      </c>
-      <c r="B66" s="2" t="s">
-        <v>98</v>
+        <v>61</v>
+      </c>
+      <c r="B66">
+        <v>2</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="B67">
-        <v>999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>69</v>
-      </c>
-      <c r="B68">
-        <v>1849</v>
+        <v>63</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>70</v>
+        <v>64</v>
+      </c>
+      <c r="B69">
+        <v>3</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>76</v>
+        <v>98</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
+        <v>66</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>67</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>68</v>
+      </c>
+      <c r="B73">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>69</v>
+      </c>
+      <c r="B74">
+        <v>1849</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>71</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
         <v>114</v>
       </c>
-      <c r="B71" t="s">
+      <c r="B77" t="s">
         <v>115</v>
       </c>
     </row>

--- a/data/gravel/Surly Karate Monkey 2025.xlsx
+++ b/data/gravel/Surly Karate Monkey 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11122"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C62EA7CF-29C3-7A46-B370-4BF999C66354}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EB88634-4019-6849-81F4-9AA6AD3937A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5980" yWindow="500" windowWidth="19740" windowHeight="16740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="124">
   <si>
     <t>brand</t>
   </si>
@@ -337,9 +337,6 @@
     <t>185.0 - 201.0</t>
   </si>
   <si>
-    <t>a8:g30</t>
-  </si>
-  <si>
     <t>Karate Monkey</t>
   </si>
   <si>
@@ -386,6 +383,15 @@
   </si>
   <si>
     <t>fork_material</t>
+  </si>
+  <si>
+    <t>a8:g32</t>
+  </si>
+  <si>
+    <t>fork_travel</t>
+  </si>
+  <si>
+    <t>fork_sag</t>
   </si>
 </sst>
 </file>
@@ -725,7 +731,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H77"/>
+  <dimension ref="A1:H79"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -744,7 +750,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
@@ -768,12 +774,12 @@
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
@@ -781,7 +787,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>105</v>
+        <v>121</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
@@ -991,7 +997,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>13</v>
       </c>
@@ -1014,7 +1020,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>15</v>
       </c>
@@ -1037,7 +1043,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>24</v>
       </c>
@@ -1060,7 +1066,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>25</v>
       </c>
@@ -1083,7 +1089,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>14</v>
       </c>
@@ -1106,7 +1112,7 @@
         <v>1158</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>23</v>
       </c>
@@ -1129,7 +1135,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>21</v>
       </c>
@@ -1152,7 +1158,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>19</v>
       </c>
@@ -1175,421 +1181,445 @@
         <v>80</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A25" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C25">
+        <v>0</v>
+      </c>
+      <c r="D25">
+        <v>0</v>
+      </c>
+      <c r="E25">
+        <v>0</v>
+      </c>
+      <c r="F25">
+        <v>0</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A26" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C26">
+        <v>0</v>
+      </c>
+      <c r="D26">
+        <v>0</v>
+      </c>
+      <c r="E26">
+        <v>0</v>
+      </c>
+      <c r="F26">
+        <v>0</v>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
         <v>27</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B28" t="s">
         <v>27</v>
       </c>
-      <c r="C26">
+      <c r="C28">
         <v>650</v>
       </c>
-      <c r="D26">
+      <c r="D28">
         <v>650</v>
       </c>
-      <c r="E26">
+      <c r="E28">
         <v>650</v>
       </c>
-      <c r="F26">
+      <c r="F28">
         <v>650</v>
       </c>
-      <c r="G26">
+      <c r="G28">
         <v>650</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
         <v>28</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B29" t="s">
         <v>28</v>
       </c>
-      <c r="C27">
+      <c r="C29">
         <v>2.8</v>
       </c>
-      <c r="D27">
+      <c r="D29">
         <v>2.8</v>
       </c>
-      <c r="E27">
+      <c r="E29">
         <v>2.8</v>
       </c>
-      <c r="F27">
+      <c r="F29">
         <v>2.8</v>
       </c>
-      <c r="G27">
+      <c r="G29">
         <v>2.8</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
         <v>29</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B30" t="s">
         <v>29</v>
       </c>
-      <c r="C28">
+      <c r="C30">
         <v>3</v>
       </c>
-      <c r="D28">
+      <c r="D30">
         <v>3</v>
       </c>
-      <c r="E28">
+      <c r="E30">
         <v>3</v>
       </c>
-      <c r="F28">
+      <c r="F30">
         <v>3</v>
       </c>
-      <c r="G28">
+      <c r="G30">
         <v>3</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
         <v>30</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B31" t="s">
         <v>31</v>
       </c>
-      <c r="C29">
+      <c r="C31">
         <v>145</v>
       </c>
-      <c r="D29">
+      <c r="D31">
         <v>155</v>
       </c>
-      <c r="E29">
+      <c r="E31">
         <v>165</v>
       </c>
-      <c r="F29">
+      <c r="F31">
         <v>175</v>
       </c>
-      <c r="G29">
+      <c r="G31">
         <v>185</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
         <v>32</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B32" t="s">
         <v>33</v>
       </c>
-      <c r="C30">
+      <c r="C32">
         <v>160</v>
       </c>
-      <c r="D30">
+      <c r="D32">
         <v>170</v>
       </c>
-      <c r="E30">
+      <c r="E32">
         <v>180</v>
       </c>
-      <c r="F30">
+      <c r="F32">
         <v>191</v>
       </c>
-      <c r="G30">
+      <c r="G32">
         <v>201</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="C31" t="s">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="C33" t="s">
         <v>100</v>
       </c>
-      <c r="D31" t="s">
+      <c r="D33" t="s">
         <v>101</v>
       </c>
-      <c r="E31" t="s">
+      <c r="E33" t="s">
         <v>102</v>
       </c>
-      <c r="F31" t="s">
+      <c r="F33" t="s">
         <v>103</v>
       </c>
-      <c r="G31" t="s">
+      <c r="G33" t="s">
         <v>104</v>
       </c>
-      <c r="H31" t="s">
+      <c r="H33" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
         <v>34</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B34" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
         <v>72</v>
       </c>
-      <c r="B33" s="2" t="s">
+      <c r="B35" s="2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>73</v>
+      </c>
+      <c r="B36" s="2" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
-        <v>73</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
         <v>74</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B37" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
         <v>36</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B38" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
         <v>40</v>
       </c>
-      <c r="B39">
+      <c r="B41">
         <v>2.5</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
         <v>41</v>
       </c>
-      <c r="B40">
+      <c r="B42">
         <v>3</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
         <v>42</v>
       </c>
-      <c r="B41">
+      <c r="B43">
         <v>120</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
         <v>46</v>
       </c>
-      <c r="B45" s="2" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A46" t="s">
+      <c r="B47" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
         <v>47</v>
       </c>
-      <c r="B46">
+      <c r="B48">
         <v>110</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A47" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A48" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>48</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>99</v>
+        <v>119</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>49</v>
+        <v>120</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>50</v>
-      </c>
-      <c r="B55">
-        <v>30.9</v>
+        <v>48</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>51</v>
-      </c>
-      <c r="B56" s="2" t="s">
-        <v>98</v>
+        <v>49</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B57">
-        <v>32</v>
+        <v>30.9</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>53</v>
-      </c>
-      <c r="B58">
-        <v>36</v>
+        <v>51</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B59">
-        <v>203</v>
+        <v>32</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B60">
-        <v>180</v>
+        <v>36</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>56</v>
+        <v>54</v>
+      </c>
+      <c r="B61">
+        <v>203</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>57</v>
-      </c>
-      <c r="B62" s="2" t="s">
-        <v>110</v>
+        <v>55</v>
+      </c>
+      <c r="B62">
+        <v>180</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>58</v>
-      </c>
-      <c r="B63" s="2" t="s">
-        <v>111</v>
+        <v>56</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>59</v>
+        <v>57</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>60</v>
+        <v>58</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>61</v>
-      </c>
-      <c r="B66">
-        <v>2</v>
+        <v>59</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>62</v>
-      </c>
-      <c r="B67">
-        <v>1</v>
+        <v>60</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>63</v>
+        <v>61</v>
+      </c>
+      <c r="B68">
+        <v>2</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B69">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>65</v>
-      </c>
-      <c r="B70" s="2" t="s">
-        <v>98</v>
+        <v>63</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>66</v>
-      </c>
-      <c r="B71" s="2" t="s">
-        <v>98</v>
+        <v>64</v>
+      </c>
+      <c r="B71">
+        <v>3</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>98</v>
@@ -1597,39 +1627,55 @@
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>68</v>
-      </c>
-      <c r="B73">
-        <v>999</v>
+        <v>66</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>69</v>
-      </c>
-      <c r="B74">
-        <v>1849</v>
+        <v>67</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>70</v>
+        <v>68</v>
+      </c>
+      <c r="B75">
+        <v>999</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>71</v>
-      </c>
-      <c r="B76" s="2" t="s">
-        <v>76</v>
+        <v>69</v>
+      </c>
+      <c r="B76">
+        <v>1849</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>71</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>113</v>
+      </c>
+      <c r="B79" t="s">
         <v>114</v>
-      </c>
-      <c r="B77" t="s">
-        <v>115</v>
       </c>
     </row>
   </sheetData>
